--- a/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
+++ b/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -748,11 +748,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -898,11 +898,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1200,9 +1200,9 @@
       <c r="I10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1270,8 +1270,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1280,37 +1282,39 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1338,17 +1342,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1378,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1408,7 +1412,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1416,47 +1420,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1481,7 +1489,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1490,24 +1498,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1524,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1554,7 +1562,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1562,47 +1570,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>1</v>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1636,11 +1648,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1670,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1709,7 +1721,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1743,12 +1755,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1776,17 +1788,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1816,12 +1828,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1846,7 +1858,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1854,51 +1866,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1923,7 +1931,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1932,24 +1940,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1966,12 +1974,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1996,7 +2004,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2004,51 +2012,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I21" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2082,11 +2086,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2116,12 +2120,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2146,7 +2150,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2154,10 +2158,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2166,39 +2168,37 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2343,12 +2343,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2384,9 +2384,9 @@
       <c r="I26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2493,12 +2493,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2532,11 +2532,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2566,12 +2566,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2682,11 +2682,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2832,11 +2832,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2943,12 +2943,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2976,17 +2976,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3016,12 +3016,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 19,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3141,15 +3141,15 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3204,8 +3204,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3214,37 +3216,39 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3280,9 +3284,9 @@
       <c r="I38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3312,12 +3316,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3342,7 +3346,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3350,8 +3354,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3360,37 +3366,39 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3418,17 +3426,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3458,12 +3466,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3488,7 +3496,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3496,8 +3504,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
-        <v>0</v>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3506,37 +3516,39 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3561,7 +3573,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 19,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3570,7 +3582,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3579,15 +3591,15 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3604,12 +3616,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3665,7 +3677,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -3677,12 +3689,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3718,9 +3730,9 @@
       <c r="I44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3750,12 +3762,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3791,9 +3803,9 @@
       <c r="I45" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3823,12 +3835,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3862,11 +3874,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3896,12 +3908,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3935,11 +3947,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3969,12 +3981,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4008,7 +4020,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4042,12 +4054,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4081,7 +4093,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4115,12 +4127,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4156,9 +4168,9 @@
       <c r="I50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4188,12 +4200,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4218,7 +4230,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4226,51 +4238,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4304,11 +4312,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4338,12 +4346,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4368,7 +4376,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4376,51 +4384,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4454,11 +4458,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4488,12 +4492,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4518,7 +4522,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4526,10 +4530,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4538,39 +4540,37 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4604,11 +4604,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4638,12 +4638,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4676,8 +4676,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4686,37 +4688,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4750,11 +4754,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4784,12 +4788,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4814,7 +4818,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4822,47 +4826,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4896,11 +4904,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4930,12 +4938,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4960,7 +4968,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4968,8 +4976,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>1</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -4978,37 +4988,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5042,11 +5054,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5076,12 +5088,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5106,7 +5118,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5114,10 +5126,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5126,39 +5136,37 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5196,7 +5204,7 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5226,12 +5234,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5256,7 +5264,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5264,51 +5272,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5342,11 +5346,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5376,12 +5380,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5406,7 +5410,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5414,10 +5418,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I67" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5426,39 +5428,37 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5492,11 +5492,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5526,12 +5526,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5603,12 +5603,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5792,11 +5792,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5942,11 +5942,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5976,12 +5976,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6094,9 +6094,9 @@
       <c r="I76" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6126,82 +6126,532 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>UTD-024-BR</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Suporte pratos organizador</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>6538166064</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>R$ 25,90</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
+++ b/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -900,9 +900,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1009,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1048,11 +1048,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,14 +1159,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1198,11 +1198,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,14 +1309,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1348,11 +1348,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1500,9 +1500,9 @@
       <c r="I14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,14 +1609,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1648,11 +1648,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1682,14 +1682,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1720,8 +1720,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1730,39 +1732,41 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1788,17 +1792,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1828,14 +1832,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1869,9 +1873,9 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1901,14 +1905,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1931,33 +1935,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1974,14 +1978,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2013,11 +2017,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2047,14 +2051,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2077,7 +2081,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2086,24 +2090,24 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2120,12 +2124,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2163,7 +2167,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2193,14 +2197,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2232,11 +2236,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2266,14 +2270,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2296,7 +2300,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2304,10 +2308,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2316,39 +2318,37 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2384,9 +2384,9 @@
       <c r="I26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2493,14 +2493,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2532,11 +2532,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2566,12 +2566,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2643,14 +2643,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2682,11 +2682,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2943,14 +2943,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2982,11 +2982,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3016,12 +3016,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3093,14 +3093,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3132,11 +3132,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3243,14 +3243,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3282,11 +3282,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3393,14 +3393,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3426,17 +3426,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3466,12 +3466,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3543,14 +3543,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 19,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
@@ -3586,20 +3586,20 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3616,14 +3616,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3654,8 +3654,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>0</v>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3664,39 +3666,41 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3719,7 +3723,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 19,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3728,7 +3732,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3737,15 +3741,15 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3762,14 +3766,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3823,7 +3827,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3835,14 +3839,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3876,9 +3880,9 @@
       <c r="I46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3908,12 +3912,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3981,14 +3985,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4020,11 +4024,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4054,12 +4058,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4127,14 +4131,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4166,11 +4170,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4200,14 +4204,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4241,9 +4245,9 @@
       <c r="I51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4273,14 +4277,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4312,11 +4316,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4346,14 +4350,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4385,11 +4389,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4419,12 +4423,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4462,7 +4466,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4492,12 +4496,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4535,7 +4539,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4565,14 +4569,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4604,7 +4608,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4638,14 +4642,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4668,7 +4672,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4676,10 +4680,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I57" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4688,39 +4690,37 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4865,14 +4865,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4906,9 +4906,9 @@
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5015,14 +5015,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5054,11 +5054,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5088,14 +5088,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5126,8 +5126,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5136,37 +5138,39 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5202,9 +5206,9 @@
       <c r="I64" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5234,14 +5238,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5275,9 +5279,9 @@
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5295,7 +5299,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5307,14 +5311,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5346,11 +5350,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5380,14 +5384,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5419,11 +5423,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5453,14 +5457,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5492,11 +5496,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5526,14 +5530,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5556,7 +5560,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5564,10 +5568,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5576,41 +5578,39 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5642,11 +5642,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5753,14 +5753,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5792,11 +5792,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5903,14 +5903,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5942,11 +5942,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5976,12 +5976,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6053,14 +6053,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6092,11 +6092,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6203,14 +6203,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6242,11 +6242,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6353,14 +6353,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6392,11 +6392,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6576,82 +6576,232 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>UTD-024-BR</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Suporte pratos organizador</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>6538166064</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>R$ 25,90</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
+++ b/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -748,11 +748,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1050,7 +1050,7 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1198,11 +1198,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1348,11 +1348,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       <c r="I16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1800,9 +1800,9 @@
       <c r="I18" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1870,8 +1870,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1880,37 +1882,39 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1938,17 +1942,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1978,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2008,7 +2012,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2016,47 +2020,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2081,7 +2089,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2090,24 +2098,24 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2124,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2154,7 +2162,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2162,47 +2170,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>1</v>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2236,11 +2248,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2270,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2309,7 +2321,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2343,12 +2355,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2376,17 +2388,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2416,12 +2428,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2446,7 +2458,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2454,51 +2466,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2523,7 +2531,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2532,24 +2540,24 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2566,12 +2574,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2596,7 +2604,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2604,51 +2612,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2682,11 +2686,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2716,12 +2720,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2746,7 +2750,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2754,10 +2758,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2766,39 +2768,37 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2943,12 +2943,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2984,9 +2984,9 @@
       <c r="I34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3016,12 +3016,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3132,11 +3132,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3282,11 +3282,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3432,11 +3432,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3466,12 +3466,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3576,17 +3576,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 19,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3741,15 +3741,15 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3766,12 +3766,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3804,8 +3804,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3814,37 +3816,39 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3880,9 +3884,9 @@
       <c r="I46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3912,12 +3916,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3942,7 +3946,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3950,8 +3954,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3960,37 +3966,39 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4018,17 +4026,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4058,12 +4066,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4088,7 +4096,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4096,8 +4104,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4106,37 +4116,39 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4161,7 +4173,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 19,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4170,7 +4182,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4179,15 +4191,15 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4204,12 +4216,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4265,7 +4277,7 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -4277,12 +4289,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4318,9 +4330,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4350,12 +4362,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4391,9 +4403,9 @@
       <c r="I53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4423,12 +4435,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4462,11 +4474,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4496,12 +4508,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4535,11 +4547,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4569,12 +4581,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4608,7 +4620,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4642,12 +4654,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4681,7 +4693,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4715,12 +4727,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4756,9 +4768,9 @@
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4788,12 +4800,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4818,7 +4830,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4826,51 +4838,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4904,11 +4912,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4938,12 +4946,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4968,7 +4976,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4976,51 +4984,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I61" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5054,11 +5058,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5088,12 +5092,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5118,7 +5122,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5126,10 +5130,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5138,39 +5140,37 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5204,11 +5204,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5276,8 +5276,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5286,37 +5288,39 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5350,11 +5354,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5384,12 +5388,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5414,7 +5418,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5422,47 +5426,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5496,11 +5504,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5530,12 +5538,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5560,7 +5568,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5568,8 +5576,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>1</v>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5578,37 +5588,39 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5642,11 +5654,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5676,12 +5688,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5706,7 +5718,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5714,10 +5726,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5726,39 +5736,37 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5794,9 +5802,9 @@
       <c r="I72" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5826,12 +5834,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5856,7 +5864,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5864,51 +5872,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5942,11 +5946,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5976,12 +5980,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6006,7 +6010,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6014,10 +6018,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6026,39 +6028,37 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6092,11 +6092,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6244,9 +6244,9 @@
       <c r="I78" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6353,12 +6353,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6392,11 +6392,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6542,11 +6542,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6694,9 +6694,9 @@
       <c r="I84" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6726,82 +6726,532 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>UTD-024-BR</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Suporte pratos organizador</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>6538166064</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>R$ 25,90</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
+++ b/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -748,11 +748,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1048,11 +1048,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1198,11 +1198,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1648,11 +1648,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1798,11 +1798,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1948,11 +1948,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       <c r="I22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
@@ -2132,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2250,9 +2250,9 @@
       <c r="I24" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2320,8 +2320,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2330,37 +2332,39 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2388,17 +2392,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2428,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2458,7 +2462,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2466,47 +2470,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2531,7 +2539,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2540,24 +2548,24 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2574,12 +2582,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2604,7 +2612,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2612,47 +2620,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>1</v>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2686,11 +2698,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2720,12 +2732,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2759,7 +2771,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2793,12 +2805,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2826,17 +2838,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2866,12 +2878,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2896,7 +2908,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2904,51 +2916,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2973,7 +2981,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2982,24 +2990,24 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3016,12 +3024,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3046,7 +3054,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3054,51 +3062,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I35" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3132,11 +3136,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3166,12 +3170,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3196,7 +3200,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3204,10 +3208,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3216,39 +3218,37 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3434,9 +3434,9 @@
       <c r="I40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3466,12 +3466,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3582,11 +3582,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3732,11 +3732,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3766,12 +3766,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3882,11 +3882,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4026,17 +4026,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4143,12 +4143,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 19,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4191,15 +4191,15 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4254,8 +4254,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4264,37 +4266,39 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4330,9 +4334,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4362,12 +4366,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4392,7 +4396,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4400,8 +4404,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4410,37 +4416,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4468,17 +4476,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4508,12 +4516,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4538,7 +4546,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4546,8 +4554,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4556,37 +4566,39 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4611,7 +4623,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 19,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4620,7 +4632,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4629,15 +4641,15 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4654,12 +4666,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4715,7 +4727,7 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4727,12 +4739,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4768,9 +4780,9 @@
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4800,12 +4812,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4841,9 +4853,9 @@
       <c r="I59" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4873,12 +4885,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4912,11 +4924,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4946,12 +4958,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4985,11 +4997,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -5019,12 +5031,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5058,7 +5070,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5092,12 +5104,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5131,7 +5143,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5165,12 +5177,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5206,9 +5218,9 @@
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5238,12 +5250,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5268,7 +5280,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5276,51 +5288,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5354,11 +5362,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5388,12 +5396,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5418,7 +5426,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5426,51 +5434,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I67" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5504,11 +5508,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5538,12 +5542,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5568,7 +5572,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5576,10 +5580,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5588,39 +5590,37 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5654,11 +5654,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5726,8 +5726,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5736,37 +5738,39 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5800,11 +5804,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5834,12 +5838,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5864,7 +5868,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5872,47 +5876,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5946,11 +5954,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5980,12 +5988,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6010,7 +6018,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6018,8 +6026,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>1</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6028,37 +6038,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6092,11 +6104,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6126,12 +6138,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6156,7 +6168,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6164,10 +6176,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6176,39 +6186,37 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6244,9 +6252,9 @@
       <c r="I78" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6276,12 +6284,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6306,7 +6314,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6314,51 +6322,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6392,11 +6396,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6426,12 +6430,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6456,7 +6460,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6464,10 +6468,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6476,39 +6478,37 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6542,11 +6542,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6694,9 +6694,9 @@
       <c r="I84" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6803,12 +6803,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6842,11 +6842,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6876,12 +6876,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6992,11 +6992,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7144,9 +7144,9 @@
       <c r="I90" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7176,82 +7176,532 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>UTD-024-BR</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Suporte pratos organizador</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>6538166064</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>R$ 25,90</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
+++ b/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,10 +670,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -682,41 +680,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -750,9 +746,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +855,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -898,11 +894,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +928,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1005,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1050,9 +1046,9 @@
       <c r="I8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1078,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,14 +1155,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1198,11 +1194,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,12 +1228,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,14 +1305,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1348,11 +1344,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1382,12 +1378,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,14 +1455,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1498,11 +1494,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1532,12 +1528,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,14 +1605,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1648,11 +1644,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1682,12 +1678,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,14 +1755,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1798,7 +1794,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1832,12 +1828,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,14 +1905,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1950,9 +1946,9 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1982,12 +1978,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,14 +2055,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2098,11 +2094,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2132,12 +2128,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,14 +2205,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2248,11 +2244,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2282,12 +2278,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,14 +2355,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2398,11 +2394,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2432,12 +2428,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,12 +2505,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2550,9 +2546,9 @@
       <c r="I28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2582,12 +2578,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2659,14 +2655,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2698,11 +2694,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2732,14 +2728,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2762,7 +2758,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2770,8 +2766,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2780,39 +2778,41 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2838,17 +2838,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2878,14 +2878,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2919,9 +2919,9 @@
       <c r="I33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2951,14 +2951,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2981,33 +2981,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3024,14 +3024,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3063,11 +3063,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3097,14 +3097,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3136,24 +3136,24 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3243,14 +3243,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3282,11 +3282,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3316,14 +3316,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3354,10 +3354,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3366,39 +3364,37 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3434,9 +3430,9 @@
       <c r="I40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3466,12 +3462,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3543,14 +3539,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3582,11 +3578,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3616,12 +3612,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3693,14 +3689,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3732,11 +3728,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3766,12 +3762,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3843,12 +3839,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3886,7 +3882,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3916,12 +3912,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3993,14 +3989,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4032,11 +4028,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4066,12 +4062,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4143,14 +4139,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4182,11 +4178,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4216,12 +4212,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4293,14 +4289,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4332,11 +4328,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4366,12 +4362,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4443,14 +4439,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4476,17 +4472,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4516,12 +4512,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4593,14 +4589,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4623,12 +4619,12 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 19,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
@@ -4636,20 +4632,20 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4666,14 +4662,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4696,7 +4692,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4704,8 +4700,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4714,39 +4712,41 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 19,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4787,15 +4787,15 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4812,14 +4812,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -4885,14 +4885,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4926,9 +4926,9 @@
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5031,14 +5031,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5070,11 +5070,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5177,14 +5177,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5216,11 +5216,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5250,14 +5250,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5291,9 +5291,9 @@
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5323,14 +5323,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5362,11 +5362,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5396,14 +5396,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5435,11 +5435,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5469,12 +5469,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5615,14 +5615,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5688,14 +5688,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5726,10 +5726,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I71" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5738,39 +5736,37 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5838,12 +5834,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5915,14 +5911,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5956,9 +5952,9 @@
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5988,12 +5984,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6065,14 +6061,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6104,11 +6100,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6138,14 +6134,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6168,7 +6164,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6176,8 +6172,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6186,37 +6184,39 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6252,9 +6252,9 @@
       <c r="I78" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6284,14 +6284,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6325,9 +6325,9 @@
       <c r="I79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6357,14 +6357,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6396,11 +6396,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6430,14 +6430,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6469,11 +6469,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6503,14 +6503,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6542,11 +6542,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6576,14 +6576,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6614,10 +6614,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6626,41 +6624,39 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6692,11 +6688,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6726,12 +6722,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6803,14 +6799,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6842,11 +6838,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6876,12 +6872,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6953,14 +6949,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6992,11 +6988,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7026,12 +7022,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7103,14 +7099,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7142,11 +7138,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7176,12 +7172,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7253,14 +7249,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7292,11 +7288,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7326,12 +7322,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7403,14 +7399,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7442,11 +7438,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7476,12 +7472,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7553,12 +7549,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7596,7 +7592,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7626,82 +7622,232 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>UTD-024-BR</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Suporte pratos organizador</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>6538166064</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>R$ 25,90</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
+++ b/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -600,9 +600,9 @@
       <c r="I2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,10 +816,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -828,39 +826,37 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -896,9 +892,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -928,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -958,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -966,10 +962,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -978,39 +972,37 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1044,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1078,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1155,12 +1147,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1194,11 +1186,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1228,12 +1220,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1305,12 +1297,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1344,11 +1336,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1378,12 +1370,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1455,12 +1447,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1496,9 +1488,9 @@
       <c r="I14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1528,12 +1520,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1605,12 +1597,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1644,11 +1636,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1678,12 +1670,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1755,12 +1747,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1828,12 +1820,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1905,12 +1897,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1946,9 +1938,9 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1978,12 +1970,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2055,12 +2047,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2094,11 +2086,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2128,12 +2120,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2205,12 +2197,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2244,11 +2236,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2278,12 +2270,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2355,12 +2347,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2394,11 +2386,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2428,12 +2420,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2505,12 +2497,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2546,9 +2538,9 @@
       <c r="I28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2578,12 +2570,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2655,12 +2647,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2694,11 +2686,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2728,12 +2720,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2805,12 +2797,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2844,11 +2836,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2878,12 +2870,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2908,7 +2900,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2916,8 +2908,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2926,37 +2920,39 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2984,17 +2980,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3024,12 +3020,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3054,7 +3050,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3062,47 +3058,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3145,15 +3145,15 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3209,11 +3209,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3276,9 +3276,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
@@ -3316,12 +3316,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3355,11 +3355,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3389,12 +3389,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3428,24 +3428,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3462,12 +3462,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3500,51 +3500,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I41" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3578,11 +3574,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3612,12 +3608,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3642,7 +3638,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3650,10 +3646,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3662,39 +3656,37 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3728,11 +3720,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3762,12 +3754,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3839,12 +3831,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3880,9 +3872,9 @@
       <c r="I46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3912,12 +3904,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3989,12 +3981,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4028,11 +4020,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4062,12 +4054,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4139,12 +4131,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4178,11 +4170,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4212,12 +4204,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4289,12 +4281,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4328,7 +4320,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4362,12 +4354,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4439,12 +4431,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4512,12 +4504,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4589,12 +4581,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4622,17 +4614,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4662,12 +4654,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4739,12 +4731,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4769,7 +4761,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 19,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4778,24 +4770,24 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4812,12 +4804,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4842,7 +4834,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4850,8 +4842,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4860,37 +4854,39 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4918,17 +4914,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4958,12 +4954,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4988,7 +4984,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4996,8 +4992,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5006,37 +5004,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 19,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5070,24 +5070,24 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5250,12 +5250,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5323,12 +5323,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5396,12 +5396,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5437,9 +5437,9 @@
       <c r="I67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5469,12 +5469,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5508,11 +5508,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5581,11 +5581,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5615,12 +5615,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5654,11 +5654,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5727,11 +5727,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5800,11 +5800,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5834,12 +5834,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5872,51 +5872,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I73" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5950,7 +5946,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -5984,12 +5980,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6014,7 +6010,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6022,10 +6018,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6034,39 +6028,37 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6102,9 +6094,9 @@
       <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6134,12 +6126,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6211,12 +6203,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6250,11 +6242,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6284,12 +6276,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6314,7 +6306,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6322,8 +6314,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6332,37 +6326,39 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6396,11 +6392,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6430,12 +6426,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6460,7 +6456,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6468,47 +6464,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6542,11 +6542,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6688,11 +6688,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6760,51 +6760,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6838,11 +6834,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6872,12 +6868,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6902,7 +6898,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6910,10 +6906,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6922,39 +6916,37 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6988,11 +6980,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7022,12 +7014,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7099,12 +7091,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7138,11 +7130,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7172,12 +7164,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7249,12 +7241,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7288,11 +7280,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7322,12 +7314,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7399,12 +7391,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7438,11 +7430,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7472,12 +7464,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7549,12 +7541,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7590,9 +7582,9 @@
       <c r="I96" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7622,12 +7614,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7699,12 +7691,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7738,11 +7730,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7772,82 +7764,382 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>UTD-024-BR</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Suporte pratos organizador</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>6538166064</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>R$ 25,90</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
+++ b/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,47 +670,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>1</v>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,7 +748,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -778,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +812,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,8 +820,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>1</v>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -826,37 +832,39 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -884,17 +892,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,7 +962,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -962,8 +970,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -972,37 +982,39 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1039,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 44,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,7 +1048,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1045,15 +1057,15 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1147,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1188,9 +1200,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1220,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1297,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1327,7 +1339,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1335,47 +1347,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>2</v>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1447,12 +1463,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1477,7 +1493,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1485,47 +1501,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1597,12 +1617,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1636,11 +1656,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1670,12 +1690,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1747,12 +1767,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1786,11 +1806,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1820,12 +1840,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1897,12 +1917,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1936,11 +1956,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1970,12 +1990,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2000,7 +2020,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2008,10 +2028,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2020,39 +2038,37 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2086,7 +2102,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2120,12 +2136,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2150,7 +2166,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2158,51 +2174,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2270,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2300,7 +2312,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2308,51 +2320,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2420,12 +2428,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2450,7 +2458,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2458,51 +2466,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2536,11 +2540,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2570,12 +2574,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2600,7 +2604,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2608,10 +2612,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2620,39 +2622,37 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2686,11 +2686,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2758,10 +2758,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2770,39 +2768,37 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2836,11 +2832,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2870,12 +2866,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2947,12 +2943,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2986,11 +2982,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3020,12 +3016,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3097,12 +3093,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3140,7 +3136,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3170,12 +3166,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3200,7 +3196,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3208,8 +3204,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3218,37 +3216,39 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3276,17 +3276,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3354,47 +3354,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3419,7 +3423,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3428,24 +3432,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3462,12 +3466,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3492,7 +3496,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3500,47 +3504,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
-        <v>1</v>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3574,11 +3582,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3608,12 +3616,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3638,7 +3646,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3646,8 +3654,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>1</v>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3656,37 +3666,39 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3720,11 +3732,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3754,12 +3766,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3831,12 +3843,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3870,11 +3882,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3904,12 +3916,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3981,12 +3993,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4020,11 +4032,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4054,12 +4066,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4131,12 +4143,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4170,11 +4182,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4204,12 +4216,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4281,12 +4293,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4322,9 +4334,9 @@
       <c r="I52" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4354,12 +4366,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4431,12 +4443,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4470,11 +4482,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4504,12 +4516,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4581,12 +4593,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4620,11 +4632,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4654,12 +4666,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4731,12 +4743,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4770,11 +4782,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4804,12 +4816,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4881,12 +4893,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4914,17 +4926,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4954,12 +4966,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4984,7 +4996,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4992,10 +5004,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5004,39 +5014,37 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5061,33 +5069,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 19,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5104,12 +5112,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5145,9 +5153,9 @@
       <c r="I63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5165,7 +5173,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5177,12 +5185,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5207,7 +5215,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5216,7 +5224,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5225,15 +5233,15 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5250,12 +5258,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5289,11 +5297,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5323,12 +5331,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5396,12 +5404,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5435,7 +5443,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5469,12 +5477,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5508,11 +5516,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5542,12 +5550,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5572,7 +5580,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5580,8 +5588,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5590,37 +5600,39 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5654,11 +5666,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5688,12 +5700,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5718,7 +5730,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5726,47 +5738,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5800,11 +5816,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5834,12 +5850,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5864,7 +5880,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5872,47 +5888,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>1</v>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5950,7 +5970,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5980,12 +6000,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6010,7 +6030,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6018,8 +6038,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>1</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6028,37 +6050,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6092,7 +6116,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6126,12 +6150,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6203,12 +6227,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6244,9 +6268,9 @@
       <c r="I78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6276,12 +6300,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6353,12 +6377,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6392,11 +6416,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6426,12 +6450,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6503,12 +6527,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6542,11 +6566,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6576,12 +6600,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6606,7 +6630,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6614,8 +6638,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6624,37 +6650,39 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6682,17 +6710,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6722,12 +6750,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6752,7 +6780,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6760,47 +6788,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6825,7 +6857,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 19,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6834,24 +6866,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6868,12 +6900,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6907,7 +6939,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6929,7 +6961,7 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6941,12 +6973,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6980,11 +7012,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7014,12 +7046,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7044,7 +7076,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7052,10 +7084,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I89" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -7064,39 +7094,37 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7130,11 +7158,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7164,12 +7192,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7194,7 +7222,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7202,10 +7230,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I91" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7214,39 +7240,37 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7280,7 +7304,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7314,12 +7338,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7344,7 +7368,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7352,10 +7376,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7364,39 +7386,37 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7464,12 +7484,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7494,7 +7514,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7502,51 +7522,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7582,9 +7598,9 @@
       <c r="I96" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7614,12 +7630,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7644,7 +7660,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7652,51 +7668,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I97" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7730,11 +7742,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7764,12 +7776,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7794,7 +7806,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7802,10 +7814,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7814,39 +7824,37 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7880,11 +7888,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7914,12 +7922,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7991,12 +7999,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8030,7 +8038,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -8064,82 +8072,1870 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>UTD-024-BR</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Suporte pratos organizador</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>6538166064</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>R$ 25,90</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
+++ b/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,51 +670,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -748,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -812,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -820,51 +816,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -892,17 +884,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -962,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -970,51 +962,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1039,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 44,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1048,24 +1036,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1112,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1120,10 +1108,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1132,39 +1118,37 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1198,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1293,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1339,59 +1323,55 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1463,12 +1443,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1493,7 +1473,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 19,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1501,51 +1481,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I14" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1617,12 +1593,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1656,11 +1632,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1690,12 +1666,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1767,12 +1743,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1806,11 +1782,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1840,12 +1816,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1870,7 +1846,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1878,10 +1854,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1890,39 +1864,37 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1956,11 +1928,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1990,12 +1962,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2031,9 +2003,9 @@
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2063,12 +2035,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2102,7 +2074,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2136,12 +2108,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2175,11 +2147,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2209,12 +2181,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2239,7 +2211,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2247,8 +2219,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2257,37 +2231,39 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2355,12 +2331,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2396,9 +2372,9 @@
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2428,12 +2404,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2471,7 +2447,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2501,12 +2477,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2540,11 +2516,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2574,12 +2550,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2604,7 +2580,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2612,8 +2588,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>1</v>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2622,37 +2600,39 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2686,7 +2666,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2720,12 +2700,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2750,7 +2730,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2758,8 +2738,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2768,37 +2750,39 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2834,9 +2818,9 @@
       <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2866,12 +2850,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2943,12 +2927,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2982,11 +2966,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3016,12 +3000,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3046,7 +3030,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3054,10 +3038,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3066,39 +3048,37 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3132,11 +3112,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3166,12 +3146,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3196,7 +3176,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3204,51 +3184,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3282,11 +3258,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3316,12 +3292,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3346,7 +3322,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3354,10 +3330,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3366,39 +3340,37 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3434,9 +3406,9 @@
       <c r="I40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3466,12 +3438,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3543,12 +3515,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3582,7 +3554,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3616,12 +3588,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3693,12 +3665,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3766,12 +3738,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3843,12 +3815,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3882,7 +3854,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3916,12 +3888,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3993,12 +3965,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4026,17 +3998,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4066,12 +4038,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4143,12 +4115,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4173,7 +4145,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 44,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4182,24 +4154,24 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4216,12 +4188,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4293,12 +4265,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4332,11 +4304,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4366,12 +4338,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4443,12 +4415,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4473,7 +4445,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4481,47 +4453,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4593,12 +4569,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4623,7 +4599,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4631,47 +4607,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>1</v>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4743,12 +4723,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4782,11 +4762,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4816,12 +4796,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4893,12 +4873,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4932,11 +4912,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4966,12 +4946,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4996,7 +4976,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5004,8 +4984,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5014,37 +4996,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5072,17 +5056,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5112,12 +5096,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5153,9 +5137,9 @@
       <c r="I63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5185,12 +5169,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5215,7 +5199,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5224,7 +5208,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5233,15 +5217,15 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5258,12 +5242,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5297,11 +5281,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5331,12 +5315,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5372,9 +5356,9 @@
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5404,12 +5388,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5447,7 +5431,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5477,12 +5461,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5516,11 +5500,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5550,12 +5534,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5580,7 +5564,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5588,51 +5572,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5666,11 +5646,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5700,12 +5680,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5730,7 +5710,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5738,10 +5718,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I71" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5750,39 +5728,37 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5816,11 +5792,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5850,12 +5826,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5880,7 +5856,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5888,10 +5864,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5900,39 +5874,37 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5966,11 +5938,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6000,12 +5972,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6077,12 +6049,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6116,11 +6088,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6150,12 +6122,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6227,12 +6199,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6266,11 +6238,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6300,12 +6272,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6377,12 +6349,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6416,11 +6388,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6450,12 +6422,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6527,12 +6499,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6566,11 +6538,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6600,12 +6572,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6677,12 +6649,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6710,17 +6682,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6750,12 +6722,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6827,12 +6799,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6857,7 +6829,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 19,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6866,24 +6838,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6900,12 +6872,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6930,7 +6902,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6938,8 +6910,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>0</v>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6948,37 +6922,39 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7012,7 +6988,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -7046,12 +7022,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7076,7 +7052,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7084,8 +7060,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>0</v>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -7094,37 +7072,39 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7160,9 +7140,9 @@
       <c r="I90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7192,12 +7172,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7222,7 +7202,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7230,8 +7210,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="n">
-        <v>0</v>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7240,37 +7222,39 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7304,11 +7288,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7338,12 +7322,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7368,7 +7352,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7376,8 +7360,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="n">
-        <v>0</v>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7386,37 +7372,39 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7450,11 +7438,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7484,12 +7472,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7514,7 +7502,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7522,47 +7510,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7596,11 +7588,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7630,12 +7622,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7660,7 +7652,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7668,47 +7660,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
-        <v>1</v>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7746,7 +7742,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7776,12 +7772,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7806,7 +7802,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7814,8 +7810,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="n">
-        <v>1</v>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7824,37 +7822,39 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7888,11 +7888,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7922,12 +7922,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7999,12 +7999,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8038,7 +8038,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -8072,12 +8072,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -8110,10 +8110,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I103" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
@@ -8122,39 +8120,37 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8182,9 +8178,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
@@ -8222,12 +8218,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8252,7 +8248,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -8260,51 +8256,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8329,7 +8321,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8338,24 +8330,24 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8372,12 +8364,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8411,11 +8403,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8433,7 +8425,7 @@
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
@@ -8445,12 +8437,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8484,11 +8476,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8518,12 +8510,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8557,11 +8549,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8591,12 +8583,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8630,11 +8622,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8664,12 +8656,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8694,7 +8686,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8702,8 +8694,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" s="2" t="n">
-        <v>1</v>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -8712,37 +8706,39 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8776,11 +8772,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8810,12 +8806,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8887,12 +8883,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8926,11 +8922,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8960,12 +8956,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9037,12 +9033,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9076,11 +9072,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9110,12 +9106,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9187,12 +9183,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9226,11 +9222,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9260,12 +9256,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9337,12 +9333,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9376,11 +9372,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9410,12 +9406,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9487,12 +9483,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9526,11 +9522,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9560,12 +9556,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9637,12 +9633,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9676,11 +9672,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9710,12 +9706,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9787,12 +9783,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9820,9 +9816,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
@@ -9830,7 +9826,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9860,82 +9856,3192 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 19,00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>UTD-024-BR</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Suporte pratos organizador</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>6538166064</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>R$ 25,90</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
+++ b/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -819,9 +819,9 @@
       <c r="I5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1182,9 +1182,9 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1254,10 +1254,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I11" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1266,41 +1264,39 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1326,15 +1322,15 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
@@ -1366,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1443,14 +1439,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1473,33 +1469,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 19,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1516,12 +1512,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1593,14 +1589,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1623,7 +1619,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 19,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1632,24 +1628,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1666,12 +1662,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1743,14 +1739,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1782,11 +1778,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1816,14 +1812,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1846,7 +1842,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1854,8 +1850,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1864,39 +1862,41 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1928,11 +1928,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1962,14 +1962,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2003,9 +2003,9 @@
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2035,14 +2035,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2074,11 +2074,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2108,14 +2108,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2147,11 +2147,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2181,14 +2181,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2219,10 +2219,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I24" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2231,39 +2229,37 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2331,14 +2327,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2361,7 +2357,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2369,8 +2365,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2379,37 +2377,39 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2477,14 +2477,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2518,9 +2518,9 @@
       <c r="I28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2550,14 +2550,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2588,10 +2588,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2600,41 +2598,39 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2666,11 +2662,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2700,12 +2696,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2777,14 +2773,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2816,11 +2812,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2850,12 +2846,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2927,14 +2923,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2966,11 +2962,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3000,14 +2996,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3030,7 +3026,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3038,8 +3034,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3048,39 +3046,41 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3112,11 +3112,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3146,14 +3146,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3187,9 +3187,9 @@
       <c r="I37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3219,14 +3219,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3258,11 +3258,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3292,14 +3292,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3331,11 +3331,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3438,14 +3438,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3476,10 +3476,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I41" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3488,39 +3486,37 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3558,7 +3554,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3588,12 +3584,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3665,14 +3661,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3704,11 +3700,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3738,12 +3734,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3815,14 +3811,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3854,11 +3850,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3888,12 +3884,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3965,14 +3961,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3998,17 +3994,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4038,12 +4034,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4115,14 +4111,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4145,33 +4141,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 44,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4188,12 +4184,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4265,14 +4261,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4295,7 +4291,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 44,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4304,7 +4300,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4313,15 +4309,15 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4338,12 +4334,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4415,14 +4411,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4445,7 +4441,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4453,10 +4449,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4465,39 +4459,37 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4569,12 +4561,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4646,12 +4638,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4723,14 +4715,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4753,7 +4745,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4761,8 +4753,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
-        <v>0</v>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4771,37 +4765,39 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4873,14 +4869,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4914,9 +4910,9 @@
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4946,12 +4942,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5023,14 +5019,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5062,11 +5058,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5096,14 +5092,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5126,7 +5122,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5134,8 +5130,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5144,37 +5142,39 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5242,14 +5242,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5283,9 +5283,9 @@
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5315,14 +5315,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5388,14 +5388,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5427,11 +5427,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5461,14 +5461,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5502,9 +5502,9 @@
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5607,14 +5607,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5646,11 +5646,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5753,14 +5753,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5826,14 +5826,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5899,12 +5899,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5972,14 +5972,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6010,10 +6010,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6022,41 +6020,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6090,9 +6086,9 @@
       <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6122,12 +6118,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6199,14 +6195,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6238,11 +6234,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6272,12 +6268,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6349,12 +6345,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6390,9 +6386,9 @@
       <c r="I80" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6422,12 +6418,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6499,14 +6495,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6538,11 +6534,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6572,12 +6568,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6649,14 +6645,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6688,11 +6684,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6722,12 +6718,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6799,14 +6795,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6838,11 +6834,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6872,12 +6868,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6949,14 +6945,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6988,11 +6984,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7022,12 +7018,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7099,14 +7095,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7138,7 +7134,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7172,12 +7168,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7249,14 +7245,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7290,9 +7286,9 @@
       <c r="I92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7322,12 +7318,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7399,14 +7395,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7438,11 +7434,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7472,12 +7468,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7549,14 +7545,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7588,11 +7584,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7622,12 +7618,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7699,14 +7695,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7738,11 +7734,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7772,12 +7768,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7849,12 +7845,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7890,9 +7886,9 @@
       <c r="I100" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7922,12 +7918,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7999,14 +7995,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8038,11 +8034,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8072,14 +8068,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8102,7 +8098,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -8110,8 +8106,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I103" s="2" t="n">
-        <v>0</v>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
@@ -8120,39 +8118,41 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8178,17 +8178,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8218,14 +8218,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8259,9 +8259,9 @@
       <c r="I105" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8291,14 +8291,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8321,33 +8321,33 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8364,14 +8364,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8403,11 +8403,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8437,14 +8437,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8467,7 +8467,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8476,24 +8476,24 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8583,14 +8583,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8622,11 +8622,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8656,14 +8656,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8694,10 +8694,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I111" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -8706,39 +8704,37 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8774,9 +8770,9 @@
       <c r="I112" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8806,12 +8802,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8883,14 +8879,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8922,11 +8918,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8956,12 +8952,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9033,14 +9029,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -9072,11 +9068,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9106,12 +9102,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9183,12 +9179,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9226,7 +9222,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9256,12 +9252,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9333,14 +9329,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -9372,11 +9368,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9406,12 +9402,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9483,14 +9479,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -9522,11 +9518,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9556,12 +9552,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9633,14 +9629,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -9672,11 +9668,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9706,12 +9702,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9783,14 +9779,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -9816,17 +9812,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H126" s="3" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9856,12 +9852,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9933,14 +9929,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -9963,12 +9959,12 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 19,00</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
@@ -9976,20 +9972,20 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10006,14 +10002,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10036,7 +10032,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -10044,8 +10040,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" s="2" t="n">
-        <v>0</v>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
@@ -10054,39 +10052,41 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 19,00</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -10127,15 +10127,15 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10152,14 +10152,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10213,7 +10213,7 @@
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
@@ -10225,14 +10225,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10266,9 +10266,9 @@
       <c r="I132" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10298,12 +10298,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10371,14 +10371,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10410,11 +10410,11 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10444,12 +10444,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10517,14 +10517,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10556,11 +10556,11 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10590,14 +10590,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10631,9 +10631,9 @@
       <c r="I137" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J137" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -10663,14 +10663,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10702,11 +10702,11 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10736,14 +10736,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10775,11 +10775,11 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J139" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -10955,14 +10955,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10994,7 +10994,7 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
@@ -11028,14 +11028,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -11066,10 +11066,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I143" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
@@ -11078,39 +11076,37 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L143" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11178,12 +11174,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11255,14 +11251,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11296,9 +11292,9 @@
       <c r="I146" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11328,12 +11324,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11405,14 +11401,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11444,11 +11440,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J148" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11478,14 +11474,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11508,7 +11504,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11516,8 +11512,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="2" t="n">
-        <v>0</v>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
@@ -11526,37 +11524,39 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11592,9 +11592,9 @@
       <c r="I150" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11624,14 +11624,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11665,9 +11665,9 @@
       <c r="I151" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
@@ -11697,14 +11697,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11736,11 +11736,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11770,14 +11770,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11809,11 +11809,11 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11843,14 +11843,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11882,11 +11882,11 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11916,14 +11916,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -11954,10 +11954,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I155" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
@@ -11966,41 +11964,39 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12032,11 +12028,11 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -12066,12 +12062,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12143,14 +12139,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12182,11 +12178,11 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J158" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12216,12 +12212,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12293,14 +12289,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12332,11 +12328,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12366,12 +12362,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12443,14 +12439,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12482,11 +12478,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12516,12 +12512,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12593,14 +12589,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12632,11 +12628,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12666,12 +12662,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12743,14 +12739,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12782,11 +12778,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J166" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12816,12 +12812,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12893,12 +12889,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -12936,7 +12932,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12966,82 +12962,232 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>UTD-024-BR</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Suporte pratos organizador</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>6538166064</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>R$ 25,90</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
+++ b/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -671,24 +671,24 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -965,9 +965,9 @@
       <c r="I7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1400,10 +1400,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1412,41 +1410,39 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1472,13 +1468,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1512,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1589,14 +1585,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1619,33 +1615,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 19,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1662,12 +1658,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1739,14 +1735,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1769,7 +1765,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 19,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1778,24 +1774,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1812,12 +1808,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1889,14 +1885,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1928,11 +1924,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1962,14 +1958,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1992,7 +1988,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2000,8 +1996,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2010,39 +2008,41 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2074,11 +2074,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2108,14 +2108,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2149,9 +2149,9 @@
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2181,14 +2181,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2220,11 +2220,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2254,14 +2254,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2293,11 +2293,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2327,14 +2327,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2365,10 +2365,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I26" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2377,39 +2375,37 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2477,14 +2473,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2507,7 +2503,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2515,8 +2511,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2525,37 +2523,39 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2623,14 +2623,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2664,9 +2664,9 @@
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2696,14 +2696,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2734,10 +2734,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2746,41 +2744,39 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2812,11 +2808,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2846,12 +2842,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2923,14 +2919,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2962,11 +2958,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2996,12 +2992,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3073,14 +3069,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3112,11 +3108,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3146,14 +3142,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3176,7 +3172,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3184,8 +3180,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3194,39 +3192,41 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3258,11 +3258,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3292,14 +3292,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3333,9 +3333,9 @@
       <c r="I39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3365,14 +3365,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3404,11 +3404,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3438,14 +3438,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3477,11 +3477,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3584,14 +3584,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3622,10 +3622,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3634,39 +3632,37 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3704,7 +3700,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3734,12 +3730,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3811,14 +3807,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3850,11 +3846,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3884,12 +3880,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3961,14 +3957,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4000,11 +3996,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4034,12 +4030,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4111,14 +4107,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4144,17 +4140,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4184,12 +4180,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4261,14 +4257,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4291,33 +4287,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 44,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4334,12 +4330,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4411,14 +4407,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4441,7 +4437,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 44,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4450,7 +4446,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4459,15 +4455,15 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4484,12 +4480,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4561,14 +4557,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4591,7 +4587,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4599,10 +4595,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4611,39 +4605,37 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4715,12 +4707,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4792,12 +4784,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4869,14 +4861,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4899,7 +4891,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4907,8 +4899,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4917,37 +4911,39 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5019,14 +5015,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5060,9 +5056,9 @@
       <c r="I62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5092,12 +5088,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5169,14 +5165,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5208,11 +5204,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5242,14 +5238,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5272,7 +5268,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5280,8 +5276,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5290,37 +5288,39 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5388,14 +5388,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5429,9 +5429,9 @@
       <c r="I67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5461,14 +5461,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5534,14 +5534,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5573,11 +5573,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5607,14 +5607,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5648,9 +5648,9 @@
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5753,14 +5753,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5792,11 +5792,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5899,14 +5899,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5938,7 +5938,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -5972,14 +5972,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6045,12 +6045,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6118,14 +6118,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6156,10 +6156,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6168,41 +6166,39 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6236,9 +6232,9 @@
       <c r="I78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6268,12 +6264,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6345,14 +6341,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6384,11 +6380,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6418,12 +6414,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6495,12 +6491,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6536,9 +6532,9 @@
       <c r="I82" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6568,12 +6564,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6645,14 +6641,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6684,11 +6680,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6718,12 +6714,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6795,14 +6791,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6834,11 +6830,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6868,12 +6864,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6945,14 +6941,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6984,11 +6980,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7018,12 +7014,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7095,14 +7091,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7134,11 +7130,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7168,12 +7164,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7245,14 +7241,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7284,7 +7280,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7318,12 +7314,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7395,14 +7391,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7436,9 +7432,9 @@
       <c r="I94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7468,12 +7464,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7545,14 +7541,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7584,11 +7580,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7618,12 +7614,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7695,14 +7691,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7734,11 +7730,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7768,12 +7764,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7845,14 +7841,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7884,11 +7880,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7918,12 +7914,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7995,12 +7991,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8036,9 +8032,9 @@
       <c r="I102" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8068,12 +8064,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8145,14 +8141,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8184,11 +8180,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8218,14 +8214,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8248,7 +8244,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -8256,8 +8252,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I105" s="2" t="n">
-        <v>0</v>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -8266,39 +8264,41 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8324,17 +8324,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H106" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8364,14 +8364,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8405,9 +8405,9 @@
       <c r="I107" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8437,14 +8437,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8467,33 +8467,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8510,14 +8510,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8549,11 +8549,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8583,14 +8583,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8622,24 +8622,24 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8656,12 +8656,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8729,14 +8729,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8768,11 +8768,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8802,14 +8802,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -8840,10 +8840,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I113" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
@@ -8852,39 +8850,37 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8920,9 +8916,9 @@
       <c r="I114" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8952,12 +8948,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9029,14 +9025,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -9068,11 +9064,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9102,12 +9098,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9179,14 +9175,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -9218,11 +9214,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9252,12 +9248,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9329,12 +9325,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9372,7 +9368,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9402,12 +9398,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9479,14 +9475,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -9518,11 +9514,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9552,12 +9548,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9629,14 +9625,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -9668,11 +9664,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9702,12 +9698,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9779,14 +9775,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -9818,11 +9814,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9852,12 +9848,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9929,14 +9925,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -9962,17 +9958,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H128" s="4" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I128" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -10002,12 +9998,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10079,14 +10075,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10109,12 +10105,12 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 19,00</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
@@ -10122,20 +10118,20 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10152,14 +10148,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10182,7 +10178,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -10190,8 +10186,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I131" s="2" t="n">
-        <v>0</v>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
@@ -10200,39 +10198,41 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L131" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 19,00</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -10273,15 +10273,15 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10298,14 +10298,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10359,7 +10359,7 @@
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
@@ -10371,14 +10371,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10412,9 +10412,9 @@
       <c r="I134" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J134" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10444,12 +10444,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10517,14 +10517,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10556,11 +10556,11 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10590,12 +10590,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10663,14 +10663,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10702,11 +10702,11 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10736,14 +10736,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10777,9 +10777,9 @@
       <c r="I139" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10809,14 +10809,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10848,11 +10848,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10882,14 +10882,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10921,11 +10921,11 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J141" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -10955,12 +10955,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -11028,12 +11028,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11101,14 +11101,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11140,7 +11140,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
@@ -11174,14 +11174,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -11212,10 +11212,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I145" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
@@ -11224,39 +11222,37 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11324,12 +11320,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11401,14 +11397,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11442,9 +11438,9 @@
       <c r="I148" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11474,12 +11470,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11551,14 +11547,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11590,11 +11586,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11624,14 +11620,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11654,7 +11650,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -11662,8 +11658,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I151" s="2" t="n">
-        <v>0</v>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -11672,37 +11670,39 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L151" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11738,9 +11738,9 @@
       <c r="I152" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11770,14 +11770,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11811,9 +11811,9 @@
       <c r="I153" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
@@ -11843,14 +11843,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11882,11 +11882,11 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11916,14 +11916,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11955,11 +11955,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11989,14 +11989,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12028,11 +12028,11 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -12062,14 +12062,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -12100,10 +12100,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I157" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
@@ -12112,41 +12110,39 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12178,11 +12174,11 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12212,12 +12208,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12289,14 +12285,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12328,11 +12324,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12362,12 +12358,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12439,14 +12435,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12478,11 +12474,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12512,12 +12508,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12589,14 +12585,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12628,11 +12624,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12662,12 +12658,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12739,14 +12735,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12778,11 +12774,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12812,12 +12808,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12889,14 +12885,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12928,11 +12924,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12962,12 +12958,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13039,12 +13035,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13082,7 +13078,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -13112,82 +13108,232 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>UTD-024-BR</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Suporte pratos organizador</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>6538166064</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>R$ 25,90</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
+++ b/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -600,9 +600,9 @@
       <c r="I2" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -817,24 +817,24 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1111,9 +1111,9 @@
       <c r="I9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1328,11 +1328,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1401,11 +1401,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1474,9 +1474,9 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1546,10 +1546,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1558,41 +1556,39 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1618,15 +1614,15 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
@@ -1658,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1735,14 +1731,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1765,33 +1761,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 19,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1808,12 +1804,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1885,14 +1881,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -1915,7 +1911,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 19,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1924,24 +1920,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1958,12 +1954,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2035,14 +2031,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2074,11 +2070,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2108,14 +2104,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2138,7 +2134,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2146,8 +2142,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2156,39 +2154,41 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2220,11 +2220,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2254,14 +2254,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2295,9 +2295,9 @@
       <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2327,14 +2327,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2366,11 +2366,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2400,14 +2400,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2439,11 +2439,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2473,14 +2473,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2511,10 +2511,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I28" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2523,39 +2521,37 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2623,14 +2619,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2653,7 +2649,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2661,8 +2657,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2671,37 +2669,39 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2769,14 +2769,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2810,9 +2810,9 @@
       <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2842,14 +2842,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2880,10 +2880,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I33" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2892,41 +2890,39 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -2958,11 +2954,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2992,12 +2988,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3069,14 +3065,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3108,11 +3104,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3142,12 +3138,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3219,14 +3215,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3258,11 +3254,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3292,14 +3288,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3322,7 +3318,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3330,8 +3326,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3340,39 +3338,41 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3404,11 +3404,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3438,14 +3438,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3479,9 +3479,9 @@
       <c r="I41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3511,14 +3511,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3550,11 +3550,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3584,14 +3584,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3623,11 +3623,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3730,14 +3730,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3768,10 +3768,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3780,39 +3778,37 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3850,7 +3846,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3880,12 +3876,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3957,14 +3953,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -3996,11 +3992,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4030,12 +4026,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4107,14 +4103,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4146,11 +4142,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4180,12 +4176,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4257,14 +4253,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4290,17 +4286,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4330,12 +4326,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4407,14 +4403,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4437,33 +4433,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 44,00</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4480,12 +4476,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4557,14 +4553,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4587,7 +4583,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 44,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4596,7 +4592,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4605,15 +4601,15 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4630,12 +4626,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4707,14 +4703,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -4737,7 +4733,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4745,10 +4741,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4757,39 +4751,37 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4861,12 +4853,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4938,12 +4930,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5015,14 +5007,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5045,7 +5037,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5053,8 +5045,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>0</v>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5063,37 +5057,39 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5165,14 +5161,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5206,9 +5202,9 @@
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5238,12 +5234,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5315,14 +5311,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5354,11 +5350,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5388,14 +5384,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5418,7 +5414,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5426,8 +5422,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5436,37 +5434,39 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5534,14 +5534,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5575,9 +5575,9 @@
       <c r="I69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5607,14 +5607,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5680,14 +5680,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5719,11 +5719,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5753,14 +5753,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5794,9 +5794,9 @@
       <c r="I72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5899,14 +5899,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -5938,11 +5938,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6045,14 +6045,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6118,14 +6118,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6191,12 +6191,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6264,14 +6264,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6302,10 +6302,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6314,41 +6312,39 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6382,9 +6378,9 @@
       <c r="I80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6414,12 +6410,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6491,14 +6487,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6530,11 +6526,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6564,12 +6560,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6641,12 +6637,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6682,9 +6678,9 @@
       <c r="I84" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6714,12 +6710,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6791,14 +6787,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6830,11 +6826,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6864,12 +6860,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6941,14 +6937,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -6980,11 +6976,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7014,12 +7010,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7091,14 +7087,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7130,11 +7126,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7164,12 +7160,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7241,14 +7237,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7280,11 +7276,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7314,12 +7310,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7391,14 +7387,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7430,7 +7426,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7464,12 +7460,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7541,14 +7537,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7582,9 +7578,9 @@
       <c r="I96" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7614,12 +7610,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7691,14 +7687,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7730,11 +7726,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7764,12 +7760,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7841,14 +7837,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -7880,11 +7876,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7914,12 +7910,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7991,14 +7987,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8030,11 +8026,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8064,12 +8060,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8141,12 +8137,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8182,9 +8178,9 @@
       <c r="I104" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8214,12 +8210,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8291,14 +8287,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8330,11 +8326,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8364,14 +8360,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8394,7 +8390,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -8402,8 +8398,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I107" s="2" t="n">
-        <v>0</v>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
@@ -8412,39 +8410,41 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8470,17 +8470,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H108" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8510,14 +8510,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8551,9 +8551,9 @@
       <c r="I109" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8583,14 +8583,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8613,33 +8613,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8656,14 +8656,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8695,11 +8695,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8729,14 +8729,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8768,24 +8768,24 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8802,12 +8802,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8875,14 +8875,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8914,11 +8914,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8948,14 +8948,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -8978,7 +8978,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -8986,10 +8986,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I115" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -8998,39 +8996,37 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9066,9 +9062,9 @@
       <c r="I116" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9098,12 +9094,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9175,14 +9171,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -9214,11 +9210,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9248,12 +9244,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9325,14 +9321,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -9364,11 +9360,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9398,12 +9394,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9475,12 +9471,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9518,7 +9514,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9548,12 +9544,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9625,14 +9621,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -9664,11 +9660,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9698,12 +9694,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9775,14 +9771,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -9814,11 +9810,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9848,12 +9844,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9925,14 +9921,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -9964,11 +9960,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9998,12 +9994,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10075,14 +10071,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10108,17 +10104,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H130" s="4" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I130" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10148,12 +10144,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10225,14 +10221,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10255,12 +10251,12 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 19,00</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
@@ -10268,20 +10264,20 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10298,14 +10294,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10328,7 +10324,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -10336,8 +10332,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I133" s="2" t="n">
-        <v>0</v>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
@@ -10346,39 +10344,41 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L133" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 19,00</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -10410,7 +10410,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10419,15 +10419,15 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10444,14 +10444,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
@@ -10517,14 +10517,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10558,9 +10558,9 @@
       <c r="I136" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J136" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10590,12 +10590,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10663,14 +10663,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10702,11 +10702,11 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10736,12 +10736,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10809,14 +10809,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10848,11 +10848,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10882,14 +10882,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10923,9 +10923,9 @@
       <c r="I141" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J141" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -10955,14 +10955,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -10994,11 +10994,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -11028,14 +11028,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11067,11 +11067,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J143" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11101,12 +11101,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11247,14 +11247,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11286,7 +11286,7 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
@@ -11320,14 +11320,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11350,7 +11350,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -11358,10 +11358,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I147" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
@@ -11370,39 +11368,37 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11470,12 +11466,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11547,14 +11543,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11588,9 +11584,9 @@
       <c r="I150" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11620,12 +11616,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11697,14 +11693,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11736,11 +11732,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11770,14 +11766,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11800,7 +11796,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -11808,8 +11804,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I153" s="2" t="n">
-        <v>0</v>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
@@ -11818,37 +11816,39 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L153" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11884,9 +11884,9 @@
       <c r="I154" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11916,14 +11916,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -11957,9 +11957,9 @@
       <c r="I155" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
@@ -11989,14 +11989,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12028,11 +12028,11 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -12062,14 +12062,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12101,11 +12101,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12135,14 +12135,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12174,11 +12174,11 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12208,14 +12208,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12246,10 +12246,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I159" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12258,41 +12256,39 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12324,11 +12320,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12358,12 +12354,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12435,14 +12431,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12474,11 +12470,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12508,12 +12504,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12585,14 +12581,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12624,11 +12620,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12658,12 +12654,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12735,14 +12731,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12774,11 +12770,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12808,12 +12804,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12885,14 +12881,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -12924,11 +12920,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12958,12 +12954,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13035,14 +13031,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-024-BR</t>
@@ -13074,11 +13070,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -13108,12 +13104,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13185,12 +13181,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13228,7 +13224,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13258,82 +13254,232 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>UTD-024-BR</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Suporte pratos organizador</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>6538166064</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>R$ 25,90</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
+++ b/saida_skus/SKU_UTD-024-BR-SUPORTE-PRATOS-ORGANIZADOR.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1184,9 +1184,9 @@
       <c r="I10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1249,17 +1249,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1328,11 +1328,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1410,15 +1410,15 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1474,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1692,51 +1692,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1764,17 +1760,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1804,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1834,7 +1830,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1842,51 +1838,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1911,7 +1903,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 19,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1920,24 +1912,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1954,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1984,7 +1976,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1992,51 +1984,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2070,11 +2058,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2104,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2134,7 +2122,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2142,10 +2130,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2154,39 +2140,37 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2220,11 +2204,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2254,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2284,7 +2268,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2292,8 +2276,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2302,37 +2288,39 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2360,17 +2348,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2400,12 +2388,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2430,7 +2418,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2438,47 +2426,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2503,7 +2495,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 19,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2512,24 +2504,24 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2546,12 +2538,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2576,7 +2568,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2584,47 +2576,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>1</v>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2649,7 +2645,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2657,51 +2653,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I30" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2726,7 +2718,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2734,47 +2726,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>1</v>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2808,11 +2804,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2842,12 +2838,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2881,7 +2877,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2915,12 +2911,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2954,11 +2950,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2988,12 +2984,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3018,7 +3014,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3026,51 +3022,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3104,7 +3096,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3138,12 +3130,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3168,7 +3160,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3176,51 +3168,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3245,7 +3233,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3253,47 +3241,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3318,7 +3310,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3326,51 +3318,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3404,11 +3392,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3438,12 +3426,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3477,7 +3465,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3511,12 +3499,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3550,11 +3538,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3584,12 +3572,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3614,7 +3602,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3622,47 +3610,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3700,7 +3692,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3730,12 +3722,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3760,7 +3752,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3768,8 +3760,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>1</v>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3778,37 +3772,39 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3842,11 +3838,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3876,12 +3872,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3953,12 +3949,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3994,9 +3990,9 @@
       <c r="I48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4026,12 +4022,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4056,7 +4052,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4064,10 +4060,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4076,39 +4070,37 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4142,11 +4134,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4176,12 +4168,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4206,7 +4198,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4214,51 +4206,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4296,7 +4284,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4326,12 +4314,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4356,7 +4344,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4364,10 +4352,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4376,39 +4362,37 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4436,17 +4420,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4476,12 +4460,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4553,12 +4537,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4583,7 +4567,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 44,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4592,7 +4576,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4601,15 +4585,15 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4626,12 +4610,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4703,12 +4687,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4744,9 +4728,9 @@
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4776,12 +4760,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4853,12 +4837,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4883,7 +4867,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4891,10 +4875,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I60" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4903,39 +4885,37 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5007,12 +4987,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5037,59 +5017,55 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5161,12 +5137,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5191,7 +5167,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 44,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5200,7 +5176,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5209,15 +5185,15 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5234,12 +5210,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5311,12 +5287,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5352,9 +5328,9 @@
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5384,12 +5360,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5461,12 +5437,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5491,7 +5467,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5499,47 +5475,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>1</v>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5564,7 +5544,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5572,8 +5552,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5582,37 +5564,39 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5637,7 +5621,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5645,8 +5629,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
-        <v>1</v>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5655,37 +5641,39 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5710,7 +5698,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5718,47 +5706,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5826,12 +5818,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5856,7 +5848,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5864,47 +5856,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>1</v>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5972,12 +5968,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6002,7 +5998,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6010,47 +6006,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>1</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6084,11 +6084,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6118,12 +6118,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6191,12 +6191,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -6264,12 +6264,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6305,9 +6305,9 @@
       <c r="I79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6337,12 +6337,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6448,51 +6448,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6560,12 +6556,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6590,7 +6586,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6598,51 +6594,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6680,7 +6672,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6710,12 +6702,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6740,7 +6732,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6748,10 +6740,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I85" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6760,39 +6750,37 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6826,11 +6814,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6860,12 +6848,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6890,7 +6878,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6898,10 +6886,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6910,39 +6896,37 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6976,11 +6960,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7010,12 +6994,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7087,12 +7071,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7126,11 +7110,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7160,12 +7144,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7237,12 +7221,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7276,11 +7260,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7310,12 +7294,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7387,12 +7371,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7428,9 +7412,9 @@
       <c r="I94" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7460,12 +7444,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7537,12 +7521,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7576,11 +7560,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7610,12 +7594,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7687,12 +7671,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7726,11 +7710,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7760,12 +7744,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7837,12 +7821,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7876,11 +7860,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7910,12 +7894,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7987,12 +7971,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8028,9 +8012,9 @@
       <c r="I102" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8060,12 +8044,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8137,12 +8121,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8176,11 +8160,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8210,12 +8194,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8287,12 +8271,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8326,11 +8310,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8360,12 +8344,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8437,12 +8421,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8476,11 +8460,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8510,12 +8494,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8540,7 +8524,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8548,8 +8532,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I109" s="2" t="n">
-        <v>0</v>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
@@ -8558,37 +8544,39 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8616,17 +8604,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8656,12 +8644,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8686,7 +8674,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8694,47 +8682,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8759,7 +8751,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 26,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8768,24 +8760,24 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8802,12 +8794,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8832,7 +8824,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -8840,47 +8832,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I113" s="2" t="n">
-        <v>1</v>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L113" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8914,11 +8910,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8948,12 +8944,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8978,7 +8974,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -8986,8 +8982,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I115" s="2" t="n">
-        <v>1</v>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -8996,37 +8994,39 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9060,11 +9060,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -9132,10 +9132,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I117" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
@@ -9144,39 +9142,37 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9204,17 +9200,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9244,12 +9240,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9274,7 +9270,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -9282,51 +9278,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9351,7 +9343,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 26,00</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -9362,22 +9354,22 @@
       <c r="I120" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9394,12 +9386,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9424,7 +9416,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9432,51 +9424,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I121" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9510,11 +9498,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9544,12 +9532,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9574,7 +9562,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9582,10 +9570,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I123" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9594,39 +9580,37 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9664,7 +9648,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9694,12 +9678,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9771,12 +9755,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9810,11 +9794,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9844,12 +9828,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9921,12 +9905,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -9960,11 +9944,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9994,12 +9978,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10071,12 +10055,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10110,11 +10094,11 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10144,12 +10128,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10221,12 +10205,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10254,9 +10238,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
@@ -10264,7 +10248,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10294,12 +10278,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10371,12 +10355,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10401,7 +10385,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 19,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -10410,24 +10394,24 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10444,12 +10428,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10474,7 +10458,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -10482,8 +10466,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I135" s="2" t="n">
-        <v>0</v>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -10492,37 +10478,39 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L135" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10556,7 +10544,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
@@ -10590,12 +10578,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10620,7 +10608,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -10628,8 +10616,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I137" s="2" t="n">
-        <v>0</v>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -10638,37 +10628,39 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L137" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10736,12 +10728,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10766,7 +10758,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -10774,8 +10766,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I139" s="2" t="n">
-        <v>0</v>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
@@ -10784,37 +10778,39 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L139" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10842,17 +10838,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10882,12 +10878,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10912,7 +10908,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -10920,8 +10916,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I141" s="2" t="n">
-        <v>0</v>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
@@ -10930,37 +10928,39 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L141" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 19,00</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -10994,24 +10994,24 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11028,12 +11028,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11069,9 +11069,9 @@
       <c r="I143" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11089,7 +11089,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O143" s="2" t="inlineStr">
@@ -11101,12 +11101,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11140,11 +11140,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11213,11 +11213,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11286,11 +11286,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11359,7 +11359,7 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
@@ -11393,12 +11393,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11432,7 +11432,7 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
@@ -11466,12 +11466,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11504,10 +11504,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I149" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
@@ -11516,39 +11514,37 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11584,9 +11580,9 @@
       <c r="I150" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11616,12 +11612,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11646,7 +11642,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -11654,51 +11650,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J151" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L151" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11732,11 +11724,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11766,12 +11758,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11796,7 +11788,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -11804,51 +11796,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I153" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11886,7 +11874,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11916,12 +11904,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -11955,7 +11943,7 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
@@ -11977,7 +11965,7 @@
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
@@ -11989,12 +11977,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12028,11 +12016,11 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -12062,12 +12050,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12092,7 +12080,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -12100,47 +12088,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12174,11 +12166,11 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12208,12 +12200,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12238,7 +12230,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12246,8 +12238,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="2" t="n">
-        <v>1</v>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12256,37 +12250,39 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12320,11 +12316,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12354,12 +12350,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12431,12 +12427,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12472,9 +12468,9 @@
       <c r="I162" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12504,12 +12500,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12534,7 +12530,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -12542,10 +12538,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I163" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
@@ -12554,39 +12548,37 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12620,11 +12612,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12654,12 +12646,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12684,7 +12676,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -12692,51 +12684,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12770,11 +12758,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12804,12 +12792,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12834,7 +12822,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -12842,10 +12830,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I167" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
@@ -12854,39 +12840,37 @@
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -12920,11 +12904,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12954,12 +12938,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13031,12 +13015,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13070,11 +13054,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J170" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -13104,12 +13088,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13181,12 +13165,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13220,11 +13204,11 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13254,12 +13238,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13331,12 +13315,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13370,11 +13354,11 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J174" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
@@ -13404,82 +13388,682 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J176" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>6538166064</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>UTD-024-BR</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Suporte pratos organizador</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>4570618893</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-024-BR</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Suporte pratos organizador</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>6538166064</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 25,90</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 25,90</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>